--- a/ExcelTemplates/StundenzettelTemplate.xlsx
+++ b/ExcelTemplates/StundenzettelTemplate.xlsx
@@ -3,20 +3,111 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Tabellenblatt1" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="Montag" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="Dienstag" sheetId="2" r:id="rId5"/>
+    <sheet state="visible" name="Mittwoch" sheetId="3" r:id="rId6"/>
+    <sheet state="visible" name="Donnerstag" sheetId="4" r:id="rId7"/>
+    <sheet state="visible" name="Freitag" sheetId="5" r:id="rId8"/>
+    <sheet state="visible" name="Wertezusammenfassung" sheetId="6" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr/>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment authorId="0" ref="D6">
+      <text>
+        <t xml:space="preserve">Kunden Zeitlich Aufgliedern wenn nötig z.B in Bayern
+</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment authorId="0" ref="D6">
+      <text>
+        <t xml:space="preserve">Kunden Zeitlich Aufgliedern wenn nötig z.B in Bayern
+</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment authorId="0" ref="D6">
+      <text>
+        <t xml:space="preserve">Kunden Zeitlich Aufgliedern wenn nötig z.B in Bayern
+</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment authorId="0" ref="D6">
+      <text>
+        <t xml:space="preserve">Kunden Zeitlich Aufgliedern wenn nötig z.B in Bayern
+</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment authorId="0" ref="D6">
+      <text>
+        <t xml:space="preserve">Kunden Zeitlich Aufgliedern wenn nötig z.B in Bayern
+</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="40">
   <si>
-    <t xml:space="preserve">Datum: </t>
+    <t>Rapportzettel :</t>
   </si>
   <si>
-    <t>2023.12.24</t>
+    <t>von</t>
+  </si>
+  <si>
+    <t>Fahrzeug :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Datum </t>
   </si>
   <si>
     <t>Beginn</t>
@@ -31,31 +122,100 @@
     <t>Kurzbeschreibung / Zweck</t>
   </si>
   <si>
+    <t>Arbeits-</t>
+  </si>
+  <si>
+    <t>Pause</t>
+  </si>
+  <si>
+    <t>Km</t>
+  </si>
+  <si>
+    <t>Dienst-</t>
+  </si>
+  <si>
+    <t>Privat-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zeit </t>
+  </si>
+  <si>
+    <t>fahrt</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Arbeitsbeschreibung:</t>
+  </si>
+  <si>
     <t>Arbeitszeit</t>
   </si>
   <si>
-    <t>Pausenzeit</t>
+    <t xml:space="preserve">Pause </t>
   </si>
   <si>
-    <t>Arbeitsbeschreibung</t>
+    <t>Gesamt km</t>
   </si>
   <si>
-    <t>Km Begin</t>
+    <t>Ge. Km</t>
   </si>
   <si>
-    <t>Km Ende</t>
+    <t xml:space="preserve">Eingang </t>
   </si>
   <si>
-    <t>Strecke</t>
+    <t xml:space="preserve">Geprüft am </t>
   </si>
   <si>
-    <t xml:space="preserve">  </t>
+    <t>Art</t>
   </si>
   <si>
-    <t>Name:</t>
+    <t>Abzug min.</t>
   </si>
   <si>
-    <t>Unterschrift:</t>
+    <t>Standard</t>
+  </si>
+  <si>
+    <t>Durch:</t>
+  </si>
+  <si>
+    <t>keine Angaben</t>
+  </si>
+  <si>
+    <t>nix</t>
+  </si>
+  <si>
+    <t>2. Prüfung</t>
+  </si>
+  <si>
+    <t>3. Prüfung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapportzettel sind jeden Freitag abzugeben bis 23:00 Uhr </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unterschrift </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monteur </t>
+  </si>
+  <si>
+    <t>Kontrolle in Ordnung :</t>
+  </si>
+  <si>
+    <t>KA</t>
+  </si>
+  <si>
+    <t>Datum:</t>
+  </si>
+  <si>
+    <t>Name des Monteurs :</t>
+  </si>
+  <si>
+    <t>Zurück bis:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">           </t>
   </si>
 </sst>
 </file>
@@ -63,87 +223,104 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="hh:mm"/>
+    <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="15">
     <font>
-      <sz val="10.0"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12.0"/>
-      <color theme="1"/>
-      <name val="Lexend"/>
     </font>
     <font>
       <b/>
       <sz val="14.0"/>
       <color theme="1"/>
-      <name val="Lexend"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="14.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
     </font>
     <font/>
     <font>
-      <sz val="18.0"/>
       <color theme="1"/>
-      <name val="Lexend"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <u/>
+      <sz val="11.0"/>
       <color theme="1"/>
-      <name val="Lexend"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <i/>
+      <u/>
+      <sz val="11.0"/>
       <color theme="1"/>
-      <name val="Lexend"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <b/>
+      <i/>
+      <u/>
+      <sz val="11.0"/>
       <color theme="1"/>
-      <name val="Lexend"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <u/>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <i/>
+      <u/>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA9999"/>
-        <bgColor rgb="FFEA9999"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFE6DD"/>
-        <bgColor rgb="FFFFE6DD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor theme="0"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="16">
@@ -230,6 +407,27 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -249,30 +447,6 @@
       </bottom>
     </border>
     <border>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thick">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-    </border>
-    <border>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -281,106 +455,149 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="74">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="2" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="6" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="3" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf borderId="3" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="center"/>
+    <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left"/>
     </xf>
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="6" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="7" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="8" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="9" fillId="0" fontId="2" numFmtId="14" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="9" fillId="0" fontId="2" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="9" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="20" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="10" fillId="0" fontId="2" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="1" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="10" fillId="0" fontId="2" numFmtId="1" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="center"/>
+      <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf borderId="2" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="9" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="9" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf borderId="11" fillId="0" fontId="4" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="10" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf borderId="9" fillId="0" fontId="4" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="11" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="9" fillId="0" fontId="4" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="12" fillId="0" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="10" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="20" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="10" fillId="0" fontId="4" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="10" fillId="0" fontId="4" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="9" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="9" fillId="0" fontId="11" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="13" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="9" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="14" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="9" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="10" fillId="0" fontId="2" numFmtId="14" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="14" fillId="0" fontId="2" numFmtId="14" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="11" fillId="0" fontId="4" numFmtId="14" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf borderId="11" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="12" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="10" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf borderId="9" fillId="0" fontId="2" numFmtId="14" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="7" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="6" fillId="0" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="7" fillId="0" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="5" fillId="0" fontId="2" numFmtId="14" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="2" fillId="0" fontId="12" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="0" fontId="13" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="14" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="12" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="10" fillId="0" fontId="14" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="15" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="13" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="9" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="13" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="9" fillId="3" fontId="7" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf borderId="14" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="11" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="5" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="8" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="7" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="5" fillId="0" fontId="2" numFmtId="14" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="9" fillId="3" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="10" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="20" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="10" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="9" fillId="4" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="9" fillId="4" fontId="7" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="9" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="13" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="5" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="13" fillId="5" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="5" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="14" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="15" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -396,12 +613,12 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="762000" cy="200025"/>
+    <xdr:ext cx="4162425" cy="847725"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.png"/>
+        <xdr:cNvPr id="0" name="image1.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -422,6 +639,142 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4162425" cy="847725"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image1.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4162425" cy="847725"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image1.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4162425" cy="847725"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image1.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4162425" cy="847725"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image1.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
@@ -439,40 +792,40 @@
         <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4285F4"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="EA4335"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="FBBC04"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="34A853"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="FF6D01"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="46BDC6"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="0000FF"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -619,838 +972,619 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="7" width="12.63"/>
-    <col customWidth="1" min="8" max="8" width="2.63"/>
-    <col customWidth="1" min="9" max="10" width="12.63"/>
-    <col customWidth="1" min="11" max="11" width="2.63"/>
+    <col customWidth="1" min="1" max="1" width="11.0"/>
+    <col customWidth="1" min="2" max="2" width="10.43"/>
+    <col customWidth="1" min="3" max="3" width="9.43"/>
+    <col customWidth="1" min="4" max="6" width="10.71"/>
+    <col customWidth="1" min="7" max="7" width="10.43"/>
+    <col customWidth="1" min="8" max="26" width="10.71"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="1"/>
-    </row>
-    <row r="2" ht="15.75" customHeight="1"/>
-    <row r="3" ht="15.75" customHeight="1"/>
-    <row r="4" ht="15.75" customHeight="1"/>
-    <row r="5" ht="15.75" customHeight="1"/>
-    <row r="6" ht="15.75" customHeight="1"/>
-    <row r="7" ht="15.75" customHeight="1"/>
-    <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-    </row>
-    <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="2" t="s">
+    <row r="4">
+      <c r="G4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="I4" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-    </row>
-    <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="7"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1"/>
-    <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="2" t="s">
+      <c r="K4" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="3"/>
+      <c r="G5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="H5" s="4"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="B6" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D12" s="5"/>
-      <c r="E12" s="12" t="s">
+      <c r="C6" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F12" s="4"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="2" t="s">
+      <c r="D6" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="J12" s="11" t="s">
+      <c r="E6" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="K12" s="14"/>
-      <c r="L12" s="15" t="s">
+      <c r="F6" s="8"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="M12" s="4"/>
-      <c r="N12" s="4"/>
-      <c r="O12" s="4"/>
-      <c r="P12" s="4"/>
-      <c r="Q12" s="4"/>
-      <c r="R12" s="5"/>
-      <c r="S12" s="14"/>
-      <c r="T12" s="2" t="s">
+      <c r="I6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="U12" s="2" t="s">
+      <c r="J6" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="V12" s="2" t="s">
+      <c r="K6" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="L6" s="8" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="7"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="14"/>
-      <c r="L13" s="8"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="9"/>
-      <c r="O13" s="9"/>
-      <c r="P13" s="9"/>
-      <c r="Q13" s="9"/>
-      <c r="R13" s="10"/>
-      <c r="S13" s="14"/>
-      <c r="T13" s="7"/>
-      <c r="U13" s="7"/>
-      <c r="V13" s="7"/>
-    </row>
-    <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="16"/>
+      <c r="M6" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="11"/>
+      <c r="J7" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L7" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="22"/>
+      <c r="J8" s="23"/>
+      <c r="K8" s="24"/>
+      <c r="L8" s="23"/>
+      <c r="M8" s="24"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="17"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="23"/>
+      <c r="K9" s="24"/>
+      <c r="L9" s="23"/>
+      <c r="M9" s="24"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="17"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="23"/>
+      <c r="K10" s="24"/>
+      <c r="L10" s="23"/>
+      <c r="M10" s="24"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="17"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="23"/>
+      <c r="K11" s="24"/>
+      <c r="L11" s="23"/>
+      <c r="M11" s="24"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="17"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="23"/>
+      <c r="K12" s="24"/>
+      <c r="L12" s="23"/>
+      <c r="M12" s="24"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="17"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="23"/>
+      <c r="K13" s="24"/>
+      <c r="L13" s="23"/>
+      <c r="M13" s="24"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="17"/>
       <c r="B14" s="16"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="17"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="18"/>
       <c r="F14" s="19"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="16"/>
-      <c r="K14" s="21"/>
-      <c r="L14" s="22"/>
-      <c r="M14" s="19"/>
-      <c r="N14" s="19"/>
-      <c r="O14" s="19"/>
-      <c r="P14" s="19"/>
-      <c r="Q14" s="19"/>
-      <c r="R14" s="18"/>
-      <c r="S14" s="21"/>
-      <c r="T14" s="16"/>
-      <c r="U14" s="16"/>
-      <c r="V14" s="16"/>
-    </row>
-    <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="23"/>
-      <c r="B15" s="24"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="25"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="23"/>
+      <c r="K14" s="24"/>
+      <c r="L14" s="23"/>
+      <c r="M14" s="24"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="17"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="18"/>
       <c r="F15" s="19"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="26"/>
-      <c r="I15" s="23"/>
-      <c r="J15" s="24"/>
-      <c r="K15" s="21"/>
-      <c r="L15" s="27"/>
-      <c r="M15" s="19"/>
-      <c r="N15" s="19"/>
-      <c r="O15" s="19"/>
-      <c r="P15" s="19"/>
-      <c r="Q15" s="19"/>
-      <c r="R15" s="18"/>
-      <c r="S15" s="21"/>
-      <c r="T15" s="23"/>
-      <c r="U15" s="23"/>
-      <c r="V15" s="23"/>
-    </row>
-    <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="28"/>
-      <c r="B16" s="29"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="17"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="24"/>
+      <c r="L15" s="23"/>
+      <c r="M15" s="24"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="17"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="18"/>
       <c r="F16" s="19"/>
-      <c r="G16" s="18"/>
-      <c r="H16" s="30"/>
-      <c r="I16" s="28"/>
-      <c r="J16" s="29"/>
-      <c r="K16" s="21"/>
-      <c r="L16" s="22"/>
-      <c r="M16" s="19"/>
-      <c r="N16" s="19"/>
-      <c r="O16" s="19"/>
-      <c r="P16" s="19"/>
-      <c r="Q16" s="19"/>
-      <c r="R16" s="18"/>
-      <c r="S16" s="21"/>
-      <c r="T16" s="28"/>
-      <c r="U16" s="28"/>
-      <c r="V16" s="28"/>
-    </row>
-    <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="23"/>
-      <c r="B17" s="23"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="25"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="23"/>
+      <c r="K16" s="24"/>
+      <c r="L16" s="23"/>
+      <c r="M16" s="24"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="17"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="18"/>
       <c r="F17" s="19"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="26"/>
-      <c r="I17" s="23"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="22"/>
       <c r="J17" s="23"/>
-      <c r="K17" s="21"/>
-      <c r="L17" s="27"/>
-      <c r="M17" s="19"/>
-      <c r="N17" s="19"/>
-      <c r="O17" s="19"/>
-      <c r="P17" s="19"/>
-      <c r="Q17" s="19"/>
-      <c r="R17" s="18"/>
-      <c r="S17" s="21"/>
-      <c r="T17" s="23"/>
-      <c r="U17" s="23"/>
-      <c r="V17" s="23"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="29"/>
-      <c r="B18" s="29"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="17"/>
+      <c r="K17" s="24"/>
+      <c r="L17" s="23"/>
+      <c r="M17" s="24"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="17"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="18"/>
       <c r="F18" s="19"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="26"/>
-      <c r="I18" s="29"/>
-      <c r="J18" s="29"/>
-      <c r="K18" s="21"/>
-      <c r="L18" s="22"/>
-      <c r="M18" s="19"/>
-      <c r="N18" s="19"/>
-      <c r="O18" s="19"/>
-      <c r="P18" s="19"/>
-      <c r="Q18" s="19"/>
-      <c r="R18" s="18"/>
-      <c r="S18" s="21"/>
-      <c r="T18" s="29"/>
-      <c r="U18" s="29"/>
-      <c r="V18" s="29"/>
-    </row>
-    <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="23"/>
-      <c r="B19" s="24"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="25"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="23"/>
+      <c r="K18" s="24"/>
+      <c r="L18" s="23"/>
+      <c r="M18" s="24"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="17"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="18"/>
       <c r="F19" s="19"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="23"/>
-      <c r="J19" s="24"/>
-      <c r="K19" s="21"/>
-      <c r="L19" s="27"/>
-      <c r="M19" s="19"/>
-      <c r="N19" s="19"/>
-      <c r="O19" s="19"/>
-      <c r="P19" s="19"/>
-      <c r="Q19" s="19"/>
-      <c r="R19" s="18"/>
-      <c r="S19" s="21"/>
-      <c r="T19" s="23"/>
-      <c r="U19" s="23"/>
-      <c r="V19" s="23"/>
-    </row>
-    <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="29"/>
-      <c r="B20" s="29"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="17"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="22"/>
+      <c r="J19" s="23"/>
+      <c r="K19" s="24"/>
+      <c r="L19" s="23"/>
+      <c r="M19" s="24"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="17"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="18"/>
       <c r="F20" s="19"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="26"/>
-      <c r="I20" s="16"/>
-      <c r="J20" s="29"/>
-      <c r="K20" s="21"/>
-      <c r="L20" s="22"/>
-      <c r="M20" s="19"/>
-      <c r="N20" s="19"/>
-      <c r="O20" s="19"/>
-      <c r="P20" s="19"/>
-      <c r="Q20" s="19"/>
-      <c r="R20" s="18"/>
-      <c r="S20" s="21"/>
-      <c r="T20" s="16"/>
-      <c r="U20" s="16"/>
-      <c r="V20" s="16"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="23"/>
+      <c r="K20" s="24"/>
+      <c r="L20" s="23"/>
+      <c r="M20" s="24"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="23"/>
-      <c r="B21" s="23"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="25"/>
+      <c r="A21" s="17"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="18"/>
       <c r="F21" s="19"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="26"/>
-      <c r="I21" s="23"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="22"/>
       <c r="J21" s="23"/>
-      <c r="K21" s="21"/>
-      <c r="L21" s="27"/>
-      <c r="M21" s="19"/>
-      <c r="N21" s="19"/>
-      <c r="O21" s="19"/>
-      <c r="P21" s="19"/>
-      <c r="Q21" s="19"/>
-      <c r="R21" s="18"/>
-      <c r="S21" s="21"/>
-      <c r="T21" s="23"/>
-      <c r="U21" s="23"/>
-      <c r="V21" s="23"/>
+      <c r="K21" s="24"/>
+      <c r="L21" s="23"/>
+      <c r="M21" s="24"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="29"/>
-      <c r="B22" s="29"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="17"/>
+      <c r="A22" s="17"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="18"/>
       <c r="F22" s="19"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="26"/>
-      <c r="I22" s="29"/>
-      <c r="J22" s="29"/>
-      <c r="K22" s="21"/>
-      <c r="L22" s="22"/>
-      <c r="M22" s="19"/>
-      <c r="N22" s="19"/>
-      <c r="O22" s="19"/>
-      <c r="P22" s="19"/>
-      <c r="Q22" s="19"/>
-      <c r="R22" s="18"/>
-      <c r="S22" s="21"/>
-      <c r="T22" s="29"/>
-      <c r="U22" s="29"/>
-      <c r="V22" s="29"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="23"/>
+      <c r="K22" s="24"/>
+      <c r="L22" s="23"/>
+      <c r="M22" s="24"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="31"/>
-      <c r="B23" s="31"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="25"/>
+      <c r="A23" s="17"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="18"/>
       <c r="F23" s="19"/>
-      <c r="G23" s="18"/>
+      <c r="G23" s="20"/>
       <c r="H23" s="21"/>
-      <c r="I23" s="31"/>
-      <c r="J23" s="31"/>
-      <c r="K23" s="21"/>
-      <c r="L23" s="27"/>
-      <c r="M23" s="19"/>
-      <c r="N23" s="19"/>
-      <c r="O23" s="19"/>
-      <c r="P23" s="19"/>
-      <c r="Q23" s="19"/>
-      <c r="R23" s="18"/>
-      <c r="S23" s="21"/>
-      <c r="T23" s="31"/>
-      <c r="U23" s="31"/>
-      <c r="V23" s="31"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="23"/>
+      <c r="K23" s="24"/>
+      <c r="L23" s="23"/>
+      <c r="M23" s="24"/>
+      <c r="Q23" s="25" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="16"/>
+      <c r="A24" s="17"/>
       <c r="B24" s="16"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="17"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="18"/>
       <c r="F24" s="19"/>
-      <c r="G24" s="18"/>
+      <c r="G24" s="20"/>
       <c r="H24" s="21"/>
-      <c r="I24" s="16"/>
-      <c r="J24" s="16"/>
-      <c r="K24" s="21"/>
-      <c r="L24" s="22"/>
-      <c r="M24" s="19"/>
-      <c r="N24" s="19"/>
-      <c r="O24" s="19"/>
-      <c r="P24" s="19"/>
-      <c r="Q24" s="19"/>
-      <c r="R24" s="18"/>
-      <c r="S24" s="21"/>
-      <c r="T24" s="16"/>
-      <c r="U24" s="16"/>
-      <c r="V24" s="16"/>
+      <c r="I24" s="22"/>
+      <c r="J24" s="23"/>
+      <c r="K24" s="24"/>
+      <c r="L24" s="23"/>
+      <c r="M24" s="24"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="31"/>
-      <c r="B25" s="31"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="25"/>
+      <c r="A25" s="17"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="18"/>
       <c r="F25" s="19"/>
-      <c r="G25" s="18"/>
+      <c r="G25" s="20"/>
       <c r="H25" s="21"/>
-      <c r="I25" s="31"/>
-      <c r="J25" s="31"/>
-      <c r="K25" s="21"/>
-      <c r="L25" s="27"/>
-      <c r="M25" s="19"/>
-      <c r="N25" s="19"/>
-      <c r="O25" s="19"/>
-      <c r="P25" s="19"/>
-      <c r="Q25" s="19"/>
-      <c r="R25" s="18"/>
-      <c r="S25" s="21"/>
-      <c r="T25" s="31"/>
-      <c r="U25" s="31"/>
-      <c r="V25" s="31"/>
+      <c r="I25" s="22"/>
+      <c r="J25" s="23"/>
+      <c r="K25" s="24"/>
+      <c r="L25" s="23"/>
+      <c r="M25" s="24"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="16"/>
+      <c r="A26" s="17"/>
       <c r="B26" s="16"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="17"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="18"/>
       <c r="F26" s="19"/>
-      <c r="G26" s="18"/>
+      <c r="G26" s="20"/>
       <c r="H26" s="21"/>
-      <c r="I26" s="16"/>
-      <c r="J26" s="16"/>
-      <c r="K26" s="21"/>
-      <c r="L26" s="22"/>
-      <c r="M26" s="19"/>
-      <c r="N26" s="19"/>
-      <c r="O26" s="19"/>
-      <c r="P26" s="19"/>
-      <c r="Q26" s="19"/>
-      <c r="R26" s="18"/>
-      <c r="S26" s="21"/>
-      <c r="T26" s="16"/>
-      <c r="U26" s="16"/>
-      <c r="V26" s="16"/>
-      <c r="Y26" s="1" t="s">
-        <v>12</v>
-      </c>
+      <c r="I26" s="22"/>
+      <c r="J26" s="23"/>
+      <c r="K26" s="24"/>
+      <c r="L26" s="23"/>
+      <c r="M26" s="24"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="31"/>
-      <c r="B27" s="31"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="25"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="18"/>
-      <c r="H27" s="21"/>
-      <c r="I27" s="31"/>
-      <c r="J27" s="31"/>
-      <c r="K27" s="21"/>
-      <c r="L27" s="27"/>
-      <c r="M27" s="19"/>
-      <c r="N27" s="19"/>
-      <c r="O27" s="19"/>
-      <c r="P27" s="19"/>
-      <c r="Q27" s="19"/>
-      <c r="R27" s="18"/>
-      <c r="S27" s="21"/>
-      <c r="T27" s="31"/>
-      <c r="U27" s="31"/>
-      <c r="V27" s="31"/>
+      <c r="A27" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B27" s="27"/>
+      <c r="C27" s="28"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="28"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="I27" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="J27" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="K27" s="33"/>
+      <c r="L27" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="M27" s="29" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="16"/>
-      <c r="B28" s="16"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="18"/>
-      <c r="H28" s="21"/>
-      <c r="I28" s="16"/>
-      <c r="J28" s="16"/>
-      <c r="K28" s="21"/>
-      <c r="L28" s="22"/>
-      <c r="M28" s="19"/>
-      <c r="N28" s="19"/>
-      <c r="O28" s="19"/>
-      <c r="P28" s="19"/>
-      <c r="Q28" s="19"/>
-      <c r="R28" s="18"/>
-      <c r="S28" s="21"/>
-      <c r="T28" s="16"/>
-      <c r="U28" s="16"/>
-      <c r="V28" s="16"/>
+      <c r="A28" s="34"/>
+      <c r="B28" s="35"/>
+      <c r="C28" s="35"/>
+      <c r="D28" s="35"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="35"/>
+      <c r="G28" s="36"/>
+      <c r="H28" s="37"/>
+      <c r="I28" s="38"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="39"/>
+      <c r="M28" s="40"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="31"/>
-      <c r="B29" s="31"/>
-      <c r="C29" s="25"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="25"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="18"/>
-      <c r="H29" s="21"/>
-      <c r="I29" s="31"/>
-      <c r="J29" s="31"/>
-      <c r="K29" s="21"/>
-      <c r="L29" s="27"/>
-      <c r="M29" s="19"/>
-      <c r="N29" s="19"/>
-      <c r="O29" s="19"/>
-      <c r="P29" s="19"/>
-      <c r="Q29" s="19"/>
-      <c r="R29" s="18"/>
-      <c r="S29" s="21"/>
-      <c r="T29" s="31"/>
-      <c r="U29" s="31"/>
-      <c r="V29" s="31"/>
+      <c r="A29" s="34"/>
+      <c r="B29" s="35"/>
+      <c r="C29" s="35"/>
+      <c r="D29" s="35"/>
+      <c r="E29" s="35"/>
+      <c r="F29" s="35"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="42"/>
+      <c r="I29" s="16"/>
+      <c r="J29" s="43"/>
+      <c r="K29" s="44"/>
+      <c r="L29" s="45"/>
+      <c r="M29" s="44"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="16"/>
-      <c r="B30" s="16"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="21"/>
-      <c r="I30" s="16"/>
-      <c r="J30" s="16"/>
-      <c r="K30" s="21"/>
-      <c r="L30" s="22"/>
-      <c r="M30" s="19"/>
-      <c r="N30" s="19"/>
-      <c r="O30" s="19"/>
-      <c r="P30" s="19"/>
-      <c r="Q30" s="19"/>
-      <c r="R30" s="18"/>
-      <c r="S30" s="21"/>
-      <c r="T30" s="16"/>
-      <c r="U30" s="16"/>
-      <c r="V30" s="16"/>
+      <c r="A30" s="34"/>
+      <c r="B30" s="35"/>
+      <c r="C30" s="35"/>
+      <c r="D30" s="35"/>
+      <c r="E30" s="35"/>
+      <c r="F30" s="35"/>
+      <c r="G30" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="H30" s="46" t="s">
+        <v>22</v>
+      </c>
+      <c r="I30" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="J30" s="47"/>
+      <c r="K30" s="36"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="29" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="31"/>
-      <c r="B31" s="31"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="25"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="21"/>
-      <c r="I31" s="31"/>
-      <c r="J31" s="31"/>
-      <c r="K31" s="21"/>
-      <c r="L31" s="27"/>
-      <c r="M31" s="19"/>
-      <c r="N31" s="19"/>
-      <c r="O31" s="19"/>
-      <c r="P31" s="19"/>
-      <c r="Q31" s="19"/>
-      <c r="R31" s="18"/>
-      <c r="S31" s="21"/>
-      <c r="T31" s="31"/>
-      <c r="U31" s="31"/>
-      <c r="V31" s="31"/>
+      <c r="A31" s="34"/>
+      <c r="B31" s="35"/>
+      <c r="C31" s="35"/>
+      <c r="D31" s="35"/>
+      <c r="E31" s="35"/>
+      <c r="F31" s="35"/>
+      <c r="G31" s="48"/>
+      <c r="H31" s="49"/>
+      <c r="I31" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="J31" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="K31" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="L31" s="51"/>
+      <c r="M31" s="29" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="16"/>
-      <c r="B32" s="16"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="21"/>
-      <c r="I32" s="16"/>
-      <c r="J32" s="16"/>
-      <c r="K32" s="21"/>
-      <c r="L32" s="22"/>
-      <c r="M32" s="19"/>
-      <c r="N32" s="19"/>
-      <c r="O32" s="19"/>
-      <c r="P32" s="19"/>
-      <c r="Q32" s="19"/>
-      <c r="R32" s="18"/>
-      <c r="S32" s="21"/>
-      <c r="T32" s="16"/>
-      <c r="U32" s="16"/>
-      <c r="V32" s="16"/>
+      <c r="A32" s="34"/>
+      <c r="B32" s="35"/>
+      <c r="C32" s="35"/>
+      <c r="D32" s="35"/>
+      <c r="E32" s="35"/>
+      <c r="F32" s="35"/>
+      <c r="G32" s="52"/>
+      <c r="H32" s="15"/>
+      <c r="I32" s="50" t="s">
+        <v>29</v>
+      </c>
+      <c r="J32" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="K32" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="L32" s="53"/>
+      <c r="M32" s="11" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="31"/>
-      <c r="B33" s="31"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="25"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="18"/>
-      <c r="H33" s="21"/>
-      <c r="I33" s="31"/>
-      <c r="J33" s="31"/>
-      <c r="K33" s="21"/>
-      <c r="L33" s="27"/>
-      <c r="M33" s="19"/>
-      <c r="N33" s="19"/>
-      <c r="O33" s="19"/>
-      <c r="P33" s="19"/>
-      <c r="Q33" s="19"/>
-      <c r="R33" s="18"/>
-      <c r="S33" s="21"/>
-      <c r="T33" s="31"/>
-      <c r="U33" s="31"/>
-      <c r="V33" s="31"/>
+      <c r="A33" s="54"/>
+      <c r="B33" s="55"/>
+      <c r="C33" s="55"/>
+      <c r="D33" s="55"/>
+      <c r="E33" s="55"/>
+      <c r="F33" s="55"/>
+      <c r="G33" s="56"/>
+      <c r="H33" s="49"/>
+      <c r="I33" s="50" t="s">
+        <v>30</v>
+      </c>
+      <c r="J33" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="K33" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="L33" s="51"/>
+      <c r="M33" s="29" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="16"/>
-      <c r="B34" s="16"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="21"/>
-      <c r="I34" s="16"/>
-      <c r="J34" s="16"/>
-      <c r="K34" s="21"/>
-      <c r="L34" s="22"/>
-      <c r="M34" s="19"/>
-      <c r="N34" s="19"/>
-      <c r="O34" s="19"/>
-      <c r="P34" s="19"/>
-      <c r="Q34" s="19"/>
-      <c r="R34" s="18"/>
-      <c r="S34" s="21"/>
-      <c r="T34" s="16"/>
-      <c r="U34" s="16"/>
-      <c r="V34" s="16"/>
+      <c r="A34" s="57" t="s">
+        <v>31</v>
+      </c>
+      <c r="B34" s="58"/>
+      <c r="C34" s="58"/>
+      <c r="D34" s="58"/>
+      <c r="E34" s="28"/>
+      <c r="F34" s="28"/>
+      <c r="G34" s="59" t="s">
+        <v>32</v>
+      </c>
+      <c r="H34" s="28"/>
+      <c r="I34" s="28"/>
+      <c r="J34" s="60"/>
+      <c r="K34" s="28"/>
+      <c r="L34" s="28"/>
+      <c r="M34" s="60"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="31"/>
-      <c r="B35" s="31"/>
-      <c r="C35" s="25"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="25"/>
-      <c r="F35" s="19"/>
-      <c r="G35" s="18"/>
-      <c r="H35" s="21"/>
-      <c r="I35" s="31"/>
-      <c r="J35" s="31"/>
-      <c r="K35" s="21"/>
-      <c r="L35" s="27"/>
-      <c r="M35" s="19"/>
-      <c r="N35" s="19"/>
-      <c r="O35" s="19"/>
-      <c r="P35" s="19"/>
-      <c r="Q35" s="19"/>
-      <c r="R35" s="18"/>
-      <c r="S35" s="21"/>
-      <c r="T35" s="31"/>
-      <c r="U35" s="31"/>
-      <c r="V35" s="31"/>
+      <c r="A35" s="61"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="62" t="s">
+        <v>33</v>
+      </c>
+      <c r="H35" s="63"/>
+      <c r="I35" s="3"/>
+      <c r="J35" s="64"/>
+      <c r="K35" s="51" t="s">
+        <v>34</v>
+      </c>
+      <c r="L35" s="51"/>
+      <c r="M35" s="29" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="16"/>
-      <c r="B36" s="16"/>
-      <c r="C36" s="17"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="19"/>
-      <c r="G36" s="18"/>
-      <c r="H36" s="20"/>
-      <c r="I36" s="16"/>
-      <c r="J36" s="16"/>
-      <c r="K36" s="21"/>
-      <c r="L36" s="22"/>
-      <c r="M36" s="19"/>
-      <c r="N36" s="19"/>
-      <c r="O36" s="19"/>
-      <c r="P36" s="19"/>
-      <c r="Q36" s="19"/>
-      <c r="R36" s="18"/>
-      <c r="S36" s="21"/>
-      <c r="T36" s="16"/>
-      <c r="U36" s="16"/>
-      <c r="V36" s="16"/>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="31"/>
-      <c r="B37" s="31"/>
-      <c r="C37" s="25"/>
-      <c r="D37" s="18"/>
-      <c r="E37" s="25"/>
-      <c r="F37" s="19"/>
-      <c r="G37" s="18"/>
-      <c r="H37" s="21"/>
-      <c r="I37" s="31"/>
-      <c r="J37" s="31"/>
-      <c r="K37" s="21"/>
-      <c r="L37" s="27"/>
-      <c r="M37" s="19"/>
-      <c r="N37" s="19"/>
-      <c r="O37" s="19"/>
-      <c r="P37" s="19"/>
-      <c r="Q37" s="19"/>
-      <c r="R37" s="18"/>
-      <c r="S37" s="21"/>
-      <c r="T37" s="31"/>
-      <c r="U37" s="31"/>
-      <c r="V37" s="31"/>
-    </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="16"/>
-      <c r="B38" s="16"/>
-      <c r="C38" s="17"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="17"/>
-      <c r="F38" s="19"/>
-      <c r="G38" s="18"/>
-      <c r="H38" s="21"/>
-      <c r="I38" s="32"/>
-      <c r="J38" s="32"/>
-      <c r="K38" s="21"/>
-      <c r="L38" s="22"/>
-      <c r="M38" s="19"/>
-      <c r="N38" s="19"/>
-      <c r="O38" s="19"/>
-      <c r="P38" s="19"/>
-      <c r="Q38" s="19"/>
-      <c r="R38" s="18"/>
-      <c r="S38" s="21"/>
-      <c r="T38" s="16"/>
-      <c r="U38" s="16"/>
-      <c r="V38" s="16"/>
-    </row>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="20"/>
-      <c r="B39" s="20"/>
-      <c r="C39" s="20"/>
-      <c r="D39" s="20"/>
-      <c r="E39" s="20"/>
-      <c r="F39" s="20"/>
-      <c r="G39" s="20"/>
-      <c r="I39" s="33"/>
-      <c r="J39" s="33"/>
-      <c r="K39" s="21"/>
-      <c r="L39" s="21"/>
-      <c r="M39" s="21"/>
-      <c r="N39" s="21"/>
-      <c r="O39" s="21"/>
-      <c r="P39" s="21"/>
-      <c r="Q39" s="21"/>
-      <c r="R39" s="21"/>
-      <c r="S39" s="21"/>
-      <c r="T39" s="34"/>
-      <c r="U39" s="34"/>
-      <c r="V39" s="35"/>
-    </row>
-    <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="36"/>
-      <c r="B40" s="36"/>
-      <c r="C40" s="36"/>
-      <c r="D40" s="36"/>
-      <c r="E40" s="36"/>
-      <c r="F40" s="36"/>
-      <c r="G40" s="36"/>
-      <c r="I40" s="7"/>
-      <c r="J40" s="7"/>
-      <c r="K40" s="21"/>
-      <c r="L40" s="21"/>
-      <c r="M40" s="21"/>
-      <c r="N40" s="21"/>
-      <c r="O40" s="21"/>
-      <c r="P40" s="21"/>
-      <c r="Q40" s="21"/>
-      <c r="R40" s="21"/>
-      <c r="S40" s="21"/>
-      <c r="T40" s="34"/>
-      <c r="U40" s="34"/>
-      <c r="V40" s="7"/>
-    </row>
+      <c r="A36" s="65" t="s">
+        <v>36</v>
+      </c>
+      <c r="B36" s="66"/>
+      <c r="C36" s="67" t="s">
+        <v>37</v>
+      </c>
+      <c r="D36" s="68"/>
+      <c r="E36" s="43"/>
+      <c r="F36" s="69"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="53"/>
+      <c r="I36" s="53"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="72" t="s">
+        <v>38</v>
+      </c>
+      <c r="L36" s="72"/>
+      <c r="M36" s="73"/>
+    </row>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="36"/>
-      <c r="B41" s="36"/>
-      <c r="C41" s="36"/>
-      <c r="D41" s="36"/>
-      <c r="E41" s="36"/>
-      <c r="F41" s="36"/>
-      <c r="G41" s="36"/>
-    </row>
-    <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="36"/>
-      <c r="B42" s="36"/>
-      <c r="C42" s="36"/>
-      <c r="D42" s="36"/>
-      <c r="E42" s="36"/>
-      <c r="F42" s="36"/>
-      <c r="G42" s="36"/>
-    </row>
-    <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="37" t="s">
-        <v>13</v>
-      </c>
-      <c r="B43" s="5"/>
-      <c r="C43" s="38"/>
-      <c r="D43" s="4"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="39"/>
-      <c r="G43" s="39"/>
-    </row>
-    <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="8"/>
-      <c r="B44" s="10"/>
-      <c r="C44" s="8"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="10"/>
-      <c r="F44" s="39"/>
-      <c r="G44" s="39"/>
-    </row>
-    <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="37" t="s">
-        <v>14</v>
-      </c>
-      <c r="B45" s="5"/>
-      <c r="C45" s="40"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="39"/>
-      <c r="G45" s="39"/>
-    </row>
-    <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="41"/>
-      <c r="B46" s="42"/>
-      <c r="C46" s="41"/>
-      <c r="E46" s="42"/>
-      <c r="F46" s="39"/>
-      <c r="G46" s="39"/>
-    </row>
-    <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="8"/>
-      <c r="B47" s="10"/>
-      <c r="C47" s="8"/>
-      <c r="D47" s="9"/>
-      <c r="E47" s="10"/>
-    </row>
+      <c r="H41" s="25" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
     <row r="48" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
@@ -2405,106 +2539,6443 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="95">
-    <mergeCell ref="L23:R23"/>
-    <mergeCell ref="L24:R24"/>
-    <mergeCell ref="L16:R16"/>
-    <mergeCell ref="L17:R17"/>
-    <mergeCell ref="L18:R18"/>
-    <mergeCell ref="L19:R19"/>
-    <mergeCell ref="L20:R20"/>
-    <mergeCell ref="L21:R21"/>
-    <mergeCell ref="L22:R22"/>
-    <mergeCell ref="L26:R26"/>
-    <mergeCell ref="L27:R27"/>
+  <mergeCells count="20">
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="E11:G11"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="E13:G13"/>
+    <mergeCell ref="E14:G14"/>
     <mergeCell ref="E22:G22"/>
     <mergeCell ref="E23:G23"/>
     <mergeCell ref="E24:G24"/>
     <mergeCell ref="E25:G25"/>
-    <mergeCell ref="L25:R25"/>
     <mergeCell ref="E26:G26"/>
-    <mergeCell ref="E27:G27"/>
-    <mergeCell ref="E28:G28"/>
-    <mergeCell ref="L28:R28"/>
-    <mergeCell ref="L29:R29"/>
-    <mergeCell ref="L30:R30"/>
-    <mergeCell ref="L31:R31"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:G30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:G31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="E32:G32"/>
-    <mergeCell ref="L32:R32"/>
-    <mergeCell ref="E33:G33"/>
-    <mergeCell ref="L33:R33"/>
-    <mergeCell ref="L34:R34"/>
-    <mergeCell ref="L35:R35"/>
-    <mergeCell ref="L36:R36"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="E34:G34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="E35:G35"/>
     <mergeCell ref="C36:D36"/>
-    <mergeCell ref="E36:G36"/>
-    <mergeCell ref="J39:J40"/>
-    <mergeCell ref="V39:V40"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="E37:G37"/>
-    <mergeCell ref="L37:R37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="E38:G38"/>
-    <mergeCell ref="L38:R38"/>
-    <mergeCell ref="I39:I40"/>
-    <mergeCell ref="I12:I13"/>
-    <mergeCell ref="J12:J13"/>
-    <mergeCell ref="L12:R13"/>
-    <mergeCell ref="T12:T13"/>
-    <mergeCell ref="U12:U13"/>
-    <mergeCell ref="V12:V13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:G14"/>
-    <mergeCell ref="L14:R14"/>
-    <mergeCell ref="A1:F7"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:D10"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:D13"/>
-    <mergeCell ref="E12:G13"/>
-    <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:G15"/>
-    <mergeCell ref="L15:R15"/>
-    <mergeCell ref="C16:D16"/>
     <mergeCell ref="E16:G16"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="E17:G17"/>
-    <mergeCell ref="C18:D18"/>
     <mergeCell ref="E18:G18"/>
-    <mergeCell ref="C19:D19"/>
     <mergeCell ref="E19:G19"/>
-    <mergeCell ref="C20:D20"/>
     <mergeCell ref="E20:G20"/>
     <mergeCell ref="E21:G21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="A43:B44"/>
-    <mergeCell ref="C43:E44"/>
-    <mergeCell ref="A45:B47"/>
-    <mergeCell ref="C45:E47"/>
   </mergeCells>
   <printOptions/>
-  <pageMargins bottom="0.5" footer="0.0" header="0.0" left="0.75" right="0.75" top="0.75"/>
-  <pageSetup orientation="landscape"/>
+  <pageMargins bottom="0.7874015748031497" footer="0.0" header="0.0" left="0.0" right="0.0" top="0.7874015748031497"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="11.0"/>
+    <col customWidth="1" min="2" max="2" width="10.43"/>
+    <col customWidth="1" min="3" max="3" width="9.43"/>
+    <col customWidth="1" min="4" max="6" width="10.71"/>
+    <col customWidth="1" min="7" max="7" width="10.43"/>
+    <col customWidth="1" min="8" max="26" width="10.71"/>
+  </cols>
+  <sheetData>
+    <row r="4">
+      <c r="G4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K4" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="3"/>
+      <c r="G5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H5" s="4"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="8"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="11"/>
+      <c r="J7" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L7" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="22"/>
+      <c r="J8" s="23"/>
+      <c r="K8" s="24"/>
+      <c r="L8" s="23"/>
+      <c r="M8" s="24"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="17"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="23"/>
+      <c r="K9" s="24"/>
+      <c r="L9" s="23"/>
+      <c r="M9" s="24"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="17"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="23"/>
+      <c r="K10" s="24"/>
+      <c r="L10" s="23"/>
+      <c r="M10" s="24"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="17"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="23"/>
+      <c r="K11" s="24"/>
+      <c r="L11" s="23"/>
+      <c r="M11" s="24"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="17"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="23"/>
+      <c r="K12" s="24"/>
+      <c r="L12" s="23"/>
+      <c r="M12" s="24"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="17"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="23"/>
+      <c r="K13" s="24"/>
+      <c r="L13" s="23"/>
+      <c r="M13" s="24"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="17"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="23"/>
+      <c r="K14" s="24"/>
+      <c r="L14" s="23"/>
+      <c r="M14" s="24"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="17"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="24"/>
+      <c r="L15" s="23"/>
+      <c r="M15" s="24"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="17"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="23"/>
+      <c r="K16" s="24"/>
+      <c r="L16" s="23"/>
+      <c r="M16" s="24"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="17"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="23"/>
+      <c r="K17" s="24"/>
+      <c r="L17" s="23"/>
+      <c r="M17" s="24"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="17"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="23"/>
+      <c r="K18" s="24"/>
+      <c r="L18" s="23"/>
+      <c r="M18" s="24"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="17"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="22"/>
+      <c r="J19" s="23"/>
+      <c r="K19" s="24"/>
+      <c r="L19" s="23"/>
+      <c r="M19" s="24"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="17"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="23"/>
+      <c r="K20" s="24"/>
+      <c r="L20" s="23"/>
+      <c r="M20" s="24"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="17"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="22"/>
+      <c r="J21" s="23"/>
+      <c r="K21" s="24"/>
+      <c r="L21" s="23"/>
+      <c r="M21" s="24"/>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="17"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="23"/>
+      <c r="K22" s="24"/>
+      <c r="L22" s="23"/>
+      <c r="M22" s="24"/>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="17"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="23"/>
+      <c r="K23" s="24"/>
+      <c r="L23" s="23"/>
+      <c r="M23" s="24"/>
+      <c r="Q23" s="25" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="17"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="22"/>
+      <c r="J24" s="23"/>
+      <c r="K24" s="24"/>
+      <c r="L24" s="23"/>
+      <c r="M24" s="24"/>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="17"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="22"/>
+      <c r="J25" s="23"/>
+      <c r="K25" s="24"/>
+      <c r="L25" s="23"/>
+      <c r="M25" s="24"/>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="17"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="23"/>
+      <c r="K26" s="24"/>
+      <c r="L26" s="23"/>
+      <c r="M26" s="24"/>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B27" s="27"/>
+      <c r="C27" s="28"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="28"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="I27" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="J27" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="K27" s="33"/>
+      <c r="L27" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="M27" s="29" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="34"/>
+      <c r="B28" s="35"/>
+      <c r="C28" s="35"/>
+      <c r="D28" s="35"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="35"/>
+      <c r="G28" s="36"/>
+      <c r="H28" s="37"/>
+      <c r="I28" s="38"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="39"/>
+      <c r="M28" s="40"/>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="34"/>
+      <c r="B29" s="35"/>
+      <c r="C29" s="35"/>
+      <c r="D29" s="35"/>
+      <c r="E29" s="35"/>
+      <c r="F29" s="35"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="42"/>
+      <c r="I29" s="16"/>
+      <c r="J29" s="43"/>
+      <c r="K29" s="44"/>
+      <c r="L29" s="45"/>
+      <c r="M29" s="44"/>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="34"/>
+      <c r="B30" s="35"/>
+      <c r="C30" s="35"/>
+      <c r="D30" s="35"/>
+      <c r="E30" s="35"/>
+      <c r="F30" s="35"/>
+      <c r="G30" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="H30" s="46" t="s">
+        <v>22</v>
+      </c>
+      <c r="I30" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="J30" s="47"/>
+      <c r="K30" s="36"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="29" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="34"/>
+      <c r="B31" s="35"/>
+      <c r="C31" s="35"/>
+      <c r="D31" s="35"/>
+      <c r="E31" s="35"/>
+      <c r="F31" s="35"/>
+      <c r="G31" s="48"/>
+      <c r="H31" s="49"/>
+      <c r="I31" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="J31" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="K31" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="L31" s="51"/>
+      <c r="M31" s="29" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="34"/>
+      <c r="B32" s="35"/>
+      <c r="C32" s="35"/>
+      <c r="D32" s="35"/>
+      <c r="E32" s="35"/>
+      <c r="F32" s="35"/>
+      <c r="G32" s="52"/>
+      <c r="H32" s="15"/>
+      <c r="I32" s="50" t="s">
+        <v>29</v>
+      </c>
+      <c r="J32" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="K32" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="L32" s="53"/>
+      <c r="M32" s="11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="54"/>
+      <c r="B33" s="55"/>
+      <c r="C33" s="55"/>
+      <c r="D33" s="55"/>
+      <c r="E33" s="55"/>
+      <c r="F33" s="55"/>
+      <c r="G33" s="56"/>
+      <c r="H33" s="49"/>
+      <c r="I33" s="50" t="s">
+        <v>30</v>
+      </c>
+      <c r="J33" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="K33" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="L33" s="51"/>
+      <c r="M33" s="29" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="57" t="s">
+        <v>31</v>
+      </c>
+      <c r="B34" s="58"/>
+      <c r="C34" s="58"/>
+      <c r="D34" s="58"/>
+      <c r="E34" s="28"/>
+      <c r="F34" s="28"/>
+      <c r="G34" s="59" t="s">
+        <v>32</v>
+      </c>
+      <c r="H34" s="28"/>
+      <c r="I34" s="28"/>
+      <c r="J34" s="60"/>
+      <c r="K34" s="28"/>
+      <c r="L34" s="28"/>
+      <c r="M34" s="60"/>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="61"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="62" t="s">
+        <v>33</v>
+      </c>
+      <c r="H35" s="63"/>
+      <c r="I35" s="3"/>
+      <c r="J35" s="64"/>
+      <c r="K35" s="51" t="s">
+        <v>34</v>
+      </c>
+      <c r="L35" s="51"/>
+      <c r="M35" s="29" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="65" t="s">
+        <v>36</v>
+      </c>
+      <c r="B36" s="66"/>
+      <c r="C36" s="67" t="s">
+        <v>37</v>
+      </c>
+      <c r="D36" s="68"/>
+      <c r="E36" s="43"/>
+      <c r="F36" s="69"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="53"/>
+      <c r="I36" s="53"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="72" t="s">
+        <v>38</v>
+      </c>
+      <c r="L36" s="72"/>
+      <c r="M36" s="73"/>
+    </row>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="H41" s="25" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="49" ht="15.75" customHeight="1"/>
+    <row r="50" ht="15.75" customHeight="1"/>
+    <row r="51" ht="15.75" customHeight="1"/>
+    <row r="52" ht="15.75" customHeight="1"/>
+    <row r="53" ht="15.75" customHeight="1"/>
+    <row r="54" ht="15.75" customHeight="1"/>
+    <row r="55" ht="15.75" customHeight="1"/>
+    <row r="56" ht="15.75" customHeight="1"/>
+    <row r="57" ht="15.75" customHeight="1"/>
+    <row r="58" ht="15.75" customHeight="1"/>
+    <row r="59" ht="15.75" customHeight="1"/>
+    <row r="60" ht="15.75" customHeight="1"/>
+    <row r="61" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1"/>
+    <row r="63" ht="15.75" customHeight="1"/>
+    <row r="64" ht="15.75" customHeight="1"/>
+    <row r="65" ht="15.75" customHeight="1"/>
+    <row r="66" ht="15.75" customHeight="1"/>
+    <row r="67" ht="15.75" customHeight="1"/>
+    <row r="68" ht="15.75" customHeight="1"/>
+    <row r="69" ht="15.75" customHeight="1"/>
+    <row r="70" ht="15.75" customHeight="1"/>
+    <row r="71" ht="15.75" customHeight="1"/>
+    <row r="72" ht="15.75" customHeight="1"/>
+    <row r="73" ht="15.75" customHeight="1"/>
+    <row r="74" ht="15.75" customHeight="1"/>
+    <row r="75" ht="15.75" customHeight="1"/>
+    <row r="76" ht="15.75" customHeight="1"/>
+    <row r="77" ht="15.75" customHeight="1"/>
+    <row r="78" ht="15.75" customHeight="1"/>
+    <row r="79" ht="15.75" customHeight="1"/>
+    <row r="80" ht="15.75" customHeight="1"/>
+    <row r="81" ht="15.75" customHeight="1"/>
+    <row r="82" ht="15.75" customHeight="1"/>
+    <row r="83" ht="15.75" customHeight="1"/>
+    <row r="84" ht="15.75" customHeight="1"/>
+    <row r="85" ht="15.75" customHeight="1"/>
+    <row r="86" ht="15.75" customHeight="1"/>
+    <row r="87" ht="15.75" customHeight="1"/>
+    <row r="88" ht="15.75" customHeight="1"/>
+    <row r="89" ht="15.75" customHeight="1"/>
+    <row r="90" ht="15.75" customHeight="1"/>
+    <row r="91" ht="15.75" customHeight="1"/>
+    <row r="92" ht="15.75" customHeight="1"/>
+    <row r="93" ht="15.75" customHeight="1"/>
+    <row r="94" ht="15.75" customHeight="1"/>
+    <row r="95" ht="15.75" customHeight="1"/>
+    <row r="96" ht="15.75" customHeight="1"/>
+    <row r="97" ht="15.75" customHeight="1"/>
+    <row r="98" ht="15.75" customHeight="1"/>
+    <row r="99" ht="15.75" customHeight="1"/>
+    <row r="100" ht="15.75" customHeight="1"/>
+    <row r="101" ht="15.75" customHeight="1"/>
+    <row r="102" ht="15.75" customHeight="1"/>
+    <row r="103" ht="15.75" customHeight="1"/>
+    <row r="104" ht="15.75" customHeight="1"/>
+    <row r="105" ht="15.75" customHeight="1"/>
+    <row r="106" ht="15.75" customHeight="1"/>
+    <row r="107" ht="15.75" customHeight="1"/>
+    <row r="108" ht="15.75" customHeight="1"/>
+    <row r="109" ht="15.75" customHeight="1"/>
+    <row r="110" ht="15.75" customHeight="1"/>
+    <row r="111" ht="15.75" customHeight="1"/>
+    <row r="112" ht="15.75" customHeight="1"/>
+    <row r="113" ht="15.75" customHeight="1"/>
+    <row r="114" ht="15.75" customHeight="1"/>
+    <row r="115" ht="15.75" customHeight="1"/>
+    <row r="116" ht="15.75" customHeight="1"/>
+    <row r="117" ht="15.75" customHeight="1"/>
+    <row r="118" ht="15.75" customHeight="1"/>
+    <row r="119" ht="15.75" customHeight="1"/>
+    <row r="120" ht="15.75" customHeight="1"/>
+    <row r="121" ht="15.75" customHeight="1"/>
+    <row r="122" ht="15.75" customHeight="1"/>
+    <row r="123" ht="15.75" customHeight="1"/>
+    <row r="124" ht="15.75" customHeight="1"/>
+    <row r="125" ht="15.75" customHeight="1"/>
+    <row r="126" ht="15.75" customHeight="1"/>
+    <row r="127" ht="15.75" customHeight="1"/>
+    <row r="128" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="20">
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="E11:G11"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="E13:G13"/>
+    <mergeCell ref="E14:G14"/>
+  </mergeCells>
+  <printOptions/>
+  <pageMargins bottom="0.7874015748031497" footer="0.0" header="0.0" left="0.0" right="0.0" top="0.7874015748031497"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="11.0"/>
+    <col customWidth="1" min="2" max="2" width="10.43"/>
+    <col customWidth="1" min="3" max="3" width="9.43"/>
+    <col customWidth="1" min="4" max="6" width="10.71"/>
+    <col customWidth="1" min="7" max="7" width="10.43"/>
+    <col customWidth="1" min="8" max="26" width="10.71"/>
+  </cols>
+  <sheetData>
+    <row r="4">
+      <c r="G4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K4" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="3"/>
+      <c r="G5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H5" s="4"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="8"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="11"/>
+      <c r="J7" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L7" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="22"/>
+      <c r="J8" s="23"/>
+      <c r="K8" s="24"/>
+      <c r="L8" s="23"/>
+      <c r="M8" s="24"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="17"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="23"/>
+      <c r="K9" s="24"/>
+      <c r="L9" s="23"/>
+      <c r="M9" s="24"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="17"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="23"/>
+      <c r="K10" s="24"/>
+      <c r="L10" s="23"/>
+      <c r="M10" s="24"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="17"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="23"/>
+      <c r="K11" s="24"/>
+      <c r="L11" s="23"/>
+      <c r="M11" s="24"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="17"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="23"/>
+      <c r="K12" s="24"/>
+      <c r="L12" s="23"/>
+      <c r="M12" s="24"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="17"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="23"/>
+      <c r="K13" s="24"/>
+      <c r="L13" s="23"/>
+      <c r="M13" s="24"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="17"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="23"/>
+      <c r="K14" s="24"/>
+      <c r="L14" s="23"/>
+      <c r="M14" s="24"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="17"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="24"/>
+      <c r="L15" s="23"/>
+      <c r="M15" s="24"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="17"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="23"/>
+      <c r="K16" s="24"/>
+      <c r="L16" s="23"/>
+      <c r="M16" s="24"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="17"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="23"/>
+      <c r="K17" s="24"/>
+      <c r="L17" s="23"/>
+      <c r="M17" s="24"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="17"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="23"/>
+      <c r="K18" s="24"/>
+      <c r="L18" s="23"/>
+      <c r="M18" s="24"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="17"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="22"/>
+      <c r="J19" s="23"/>
+      <c r="K19" s="24"/>
+      <c r="L19" s="23"/>
+      <c r="M19" s="24"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="17"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="23"/>
+      <c r="K20" s="24"/>
+      <c r="L20" s="23"/>
+      <c r="M20" s="24"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="17"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="22"/>
+      <c r="J21" s="23"/>
+      <c r="K21" s="24"/>
+      <c r="L21" s="23"/>
+      <c r="M21" s="24"/>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="17"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="23"/>
+      <c r="K22" s="24"/>
+      <c r="L22" s="23"/>
+      <c r="M22" s="24"/>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="17"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="23"/>
+      <c r="K23" s="24"/>
+      <c r="L23" s="23"/>
+      <c r="M23" s="24"/>
+      <c r="Q23" s="25" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="17"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="22"/>
+      <c r="J24" s="23"/>
+      <c r="K24" s="24"/>
+      <c r="L24" s="23"/>
+      <c r="M24" s="24"/>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="17"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="22"/>
+      <c r="J25" s="23"/>
+      <c r="K25" s="24"/>
+      <c r="L25" s="23"/>
+      <c r="M25" s="24"/>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="17"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="23"/>
+      <c r="K26" s="24"/>
+      <c r="L26" s="23"/>
+      <c r="M26" s="24"/>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B27" s="27"/>
+      <c r="C27" s="28"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="28"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="I27" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="J27" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="K27" s="33"/>
+      <c r="L27" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="M27" s="29" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="34"/>
+      <c r="B28" s="35"/>
+      <c r="C28" s="35"/>
+      <c r="D28" s="35"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="35"/>
+      <c r="G28" s="36"/>
+      <c r="H28" s="37"/>
+      <c r="I28" s="38"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="39"/>
+      <c r="M28" s="40"/>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="34"/>
+      <c r="B29" s="35"/>
+      <c r="C29" s="35"/>
+      <c r="D29" s="35"/>
+      <c r="E29" s="35"/>
+      <c r="F29" s="35"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="42"/>
+      <c r="I29" s="16"/>
+      <c r="J29" s="43"/>
+      <c r="K29" s="44"/>
+      <c r="L29" s="45"/>
+      <c r="M29" s="44"/>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="34"/>
+      <c r="B30" s="35"/>
+      <c r="C30" s="35"/>
+      <c r="D30" s="35"/>
+      <c r="E30" s="35"/>
+      <c r="F30" s="35"/>
+      <c r="G30" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="H30" s="46" t="s">
+        <v>22</v>
+      </c>
+      <c r="I30" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="J30" s="47"/>
+      <c r="K30" s="36"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="29" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="34"/>
+      <c r="B31" s="35"/>
+      <c r="C31" s="35"/>
+      <c r="D31" s="35"/>
+      <c r="E31" s="35"/>
+      <c r="F31" s="35"/>
+      <c r="G31" s="48"/>
+      <c r="H31" s="49"/>
+      <c r="I31" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="J31" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="K31" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="L31" s="51"/>
+      <c r="M31" s="29" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="34"/>
+      <c r="B32" s="35"/>
+      <c r="C32" s="35"/>
+      <c r="D32" s="35"/>
+      <c r="E32" s="35"/>
+      <c r="F32" s="35"/>
+      <c r="G32" s="52"/>
+      <c r="H32" s="15"/>
+      <c r="I32" s="50" t="s">
+        <v>29</v>
+      </c>
+      <c r="J32" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="K32" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="L32" s="53"/>
+      <c r="M32" s="11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="54"/>
+      <c r="B33" s="55"/>
+      <c r="C33" s="55"/>
+      <c r="D33" s="55"/>
+      <c r="E33" s="55"/>
+      <c r="F33" s="55"/>
+      <c r="G33" s="56"/>
+      <c r="H33" s="49"/>
+      <c r="I33" s="50" t="s">
+        <v>30</v>
+      </c>
+      <c r="J33" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="K33" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="L33" s="51"/>
+      <c r="M33" s="29" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="57" t="s">
+        <v>31</v>
+      </c>
+      <c r="B34" s="58"/>
+      <c r="C34" s="58"/>
+      <c r="D34" s="58"/>
+      <c r="E34" s="28"/>
+      <c r="F34" s="28"/>
+      <c r="G34" s="59" t="s">
+        <v>32</v>
+      </c>
+      <c r="H34" s="28"/>
+      <c r="I34" s="28"/>
+      <c r="J34" s="60"/>
+      <c r="K34" s="28"/>
+      <c r="L34" s="28"/>
+      <c r="M34" s="60"/>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="61"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="62" t="s">
+        <v>33</v>
+      </c>
+      <c r="H35" s="63"/>
+      <c r="I35" s="3"/>
+      <c r="J35" s="64"/>
+      <c r="K35" s="51" t="s">
+        <v>34</v>
+      </c>
+      <c r="L35" s="51"/>
+      <c r="M35" s="29" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="65" t="s">
+        <v>36</v>
+      </c>
+      <c r="B36" s="66"/>
+      <c r="C36" s="67" t="s">
+        <v>37</v>
+      </c>
+      <c r="D36" s="68"/>
+      <c r="E36" s="43"/>
+      <c r="F36" s="69"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="53"/>
+      <c r="I36" s="53"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="72" t="s">
+        <v>38</v>
+      </c>
+      <c r="L36" s="72"/>
+      <c r="M36" s="73"/>
+    </row>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="H41" s="25" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="49" ht="15.75" customHeight="1"/>
+    <row r="50" ht="15.75" customHeight="1"/>
+    <row r="51" ht="15.75" customHeight="1"/>
+    <row r="52" ht="15.75" customHeight="1"/>
+    <row r="53" ht="15.75" customHeight="1"/>
+    <row r="54" ht="15.75" customHeight="1"/>
+    <row r="55" ht="15.75" customHeight="1"/>
+    <row r="56" ht="15.75" customHeight="1"/>
+    <row r="57" ht="15.75" customHeight="1"/>
+    <row r="58" ht="15.75" customHeight="1"/>
+    <row r="59" ht="15.75" customHeight="1"/>
+    <row r="60" ht="15.75" customHeight="1"/>
+    <row r="61" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1"/>
+    <row r="63" ht="15.75" customHeight="1"/>
+    <row r="64" ht="15.75" customHeight="1"/>
+    <row r="65" ht="15.75" customHeight="1"/>
+    <row r="66" ht="15.75" customHeight="1"/>
+    <row r="67" ht="15.75" customHeight="1"/>
+    <row r="68" ht="15.75" customHeight="1"/>
+    <row r="69" ht="15.75" customHeight="1"/>
+    <row r="70" ht="15.75" customHeight="1"/>
+    <row r="71" ht="15.75" customHeight="1"/>
+    <row r="72" ht="15.75" customHeight="1"/>
+    <row r="73" ht="15.75" customHeight="1"/>
+    <row r="74" ht="15.75" customHeight="1"/>
+    <row r="75" ht="15.75" customHeight="1"/>
+    <row r="76" ht="15.75" customHeight="1"/>
+    <row r="77" ht="15.75" customHeight="1"/>
+    <row r="78" ht="15.75" customHeight="1"/>
+    <row r="79" ht="15.75" customHeight="1"/>
+    <row r="80" ht="15.75" customHeight="1"/>
+    <row r="81" ht="15.75" customHeight="1"/>
+    <row r="82" ht="15.75" customHeight="1"/>
+    <row r="83" ht="15.75" customHeight="1"/>
+    <row r="84" ht="15.75" customHeight="1"/>
+    <row r="85" ht="15.75" customHeight="1"/>
+    <row r="86" ht="15.75" customHeight="1"/>
+    <row r="87" ht="15.75" customHeight="1"/>
+    <row r="88" ht="15.75" customHeight="1"/>
+    <row r="89" ht="15.75" customHeight="1"/>
+    <row r="90" ht="15.75" customHeight="1"/>
+    <row r="91" ht="15.75" customHeight="1"/>
+    <row r="92" ht="15.75" customHeight="1"/>
+    <row r="93" ht="15.75" customHeight="1"/>
+    <row r="94" ht="15.75" customHeight="1"/>
+    <row r="95" ht="15.75" customHeight="1"/>
+    <row r="96" ht="15.75" customHeight="1"/>
+    <row r="97" ht="15.75" customHeight="1"/>
+    <row r="98" ht="15.75" customHeight="1"/>
+    <row r="99" ht="15.75" customHeight="1"/>
+    <row r="100" ht="15.75" customHeight="1"/>
+    <row r="101" ht="15.75" customHeight="1"/>
+    <row r="102" ht="15.75" customHeight="1"/>
+    <row r="103" ht="15.75" customHeight="1"/>
+    <row r="104" ht="15.75" customHeight="1"/>
+    <row r="105" ht="15.75" customHeight="1"/>
+    <row r="106" ht="15.75" customHeight="1"/>
+    <row r="107" ht="15.75" customHeight="1"/>
+    <row r="108" ht="15.75" customHeight="1"/>
+    <row r="109" ht="15.75" customHeight="1"/>
+    <row r="110" ht="15.75" customHeight="1"/>
+    <row r="111" ht="15.75" customHeight="1"/>
+    <row r="112" ht="15.75" customHeight="1"/>
+    <row r="113" ht="15.75" customHeight="1"/>
+    <row r="114" ht="15.75" customHeight="1"/>
+    <row r="115" ht="15.75" customHeight="1"/>
+    <row r="116" ht="15.75" customHeight="1"/>
+    <row r="117" ht="15.75" customHeight="1"/>
+    <row r="118" ht="15.75" customHeight="1"/>
+    <row r="119" ht="15.75" customHeight="1"/>
+    <row r="120" ht="15.75" customHeight="1"/>
+    <row r="121" ht="15.75" customHeight="1"/>
+    <row r="122" ht="15.75" customHeight="1"/>
+    <row r="123" ht="15.75" customHeight="1"/>
+    <row r="124" ht="15.75" customHeight="1"/>
+    <row r="125" ht="15.75" customHeight="1"/>
+    <row r="126" ht="15.75" customHeight="1"/>
+    <row r="127" ht="15.75" customHeight="1"/>
+    <row r="128" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="20">
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="E11:G11"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="E13:G13"/>
+    <mergeCell ref="E14:G14"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="E8:G8"/>
+  </mergeCells>
+  <printOptions/>
+  <pageMargins bottom="0.7874015748031497" footer="0.0" header="0.0" left="0.0" right="0.0" top="0.7874015748031497"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="11.0"/>
+    <col customWidth="1" min="2" max="2" width="10.43"/>
+    <col customWidth="1" min="3" max="3" width="9.43"/>
+    <col customWidth="1" min="4" max="6" width="10.71"/>
+    <col customWidth="1" min="7" max="7" width="10.43"/>
+    <col customWidth="1" min="8" max="26" width="10.71"/>
+  </cols>
+  <sheetData>
+    <row r="4">
+      <c r="G4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K4" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="3"/>
+      <c r="G5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H5" s="4"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="8"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="11"/>
+      <c r="J7" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L7" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="22"/>
+      <c r="J8" s="23"/>
+      <c r="K8" s="24"/>
+      <c r="L8" s="23"/>
+      <c r="M8" s="24"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="17"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="23"/>
+      <c r="K9" s="24"/>
+      <c r="L9" s="23"/>
+      <c r="M9" s="24"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="17"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="23"/>
+      <c r="K10" s="24"/>
+      <c r="L10" s="23"/>
+      <c r="M10" s="24"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="17"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="23"/>
+      <c r="K11" s="24"/>
+      <c r="L11" s="23"/>
+      <c r="M11" s="24"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="17"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="23"/>
+      <c r="K12" s="24"/>
+      <c r="L12" s="23"/>
+      <c r="M12" s="24"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="17"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="23"/>
+      <c r="K13" s="24"/>
+      <c r="L13" s="23"/>
+      <c r="M13" s="24"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="17"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="23"/>
+      <c r="K14" s="24"/>
+      <c r="L14" s="23"/>
+      <c r="M14" s="24"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="17"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="24"/>
+      <c r="L15" s="23"/>
+      <c r="M15" s="24"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="17"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="23"/>
+      <c r="K16" s="24"/>
+      <c r="L16" s="23"/>
+      <c r="M16" s="24"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="17"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="23"/>
+      <c r="K17" s="24"/>
+      <c r="L17" s="23"/>
+      <c r="M17" s="24"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="17"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="23"/>
+      <c r="K18" s="24"/>
+      <c r="L18" s="23"/>
+      <c r="M18" s="24"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="17"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="22"/>
+      <c r="J19" s="23"/>
+      <c r="K19" s="24"/>
+      <c r="L19" s="23"/>
+      <c r="M19" s="24"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="17"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="23"/>
+      <c r="K20" s="24"/>
+      <c r="L20" s="23"/>
+      <c r="M20" s="24"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="17"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="22"/>
+      <c r="J21" s="23"/>
+      <c r="K21" s="24"/>
+      <c r="L21" s="23"/>
+      <c r="M21" s="24"/>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="17"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="23"/>
+      <c r="K22" s="24"/>
+      <c r="L22" s="23"/>
+      <c r="M22" s="24"/>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="17"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="23"/>
+      <c r="K23" s="24"/>
+      <c r="L23" s="23"/>
+      <c r="M23" s="24"/>
+      <c r="Q23" s="25" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="17"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="22"/>
+      <c r="J24" s="23"/>
+      <c r="K24" s="24"/>
+      <c r="L24" s="23"/>
+      <c r="M24" s="24"/>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="17"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="22"/>
+      <c r="J25" s="23"/>
+      <c r="K25" s="24"/>
+      <c r="L25" s="23"/>
+      <c r="M25" s="24"/>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="17"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="23"/>
+      <c r="K26" s="24"/>
+      <c r="L26" s="23"/>
+      <c r="M26" s="24"/>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B27" s="27"/>
+      <c r="C27" s="28"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="28"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="I27" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="J27" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="K27" s="33"/>
+      <c r="L27" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="M27" s="29" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="34"/>
+      <c r="B28" s="35"/>
+      <c r="C28" s="35"/>
+      <c r="D28" s="35"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="35"/>
+      <c r="G28" s="36"/>
+      <c r="H28" s="37"/>
+      <c r="I28" s="38"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="39"/>
+      <c r="M28" s="40"/>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="34"/>
+      <c r="B29" s="35"/>
+      <c r="C29" s="35"/>
+      <c r="D29" s="35"/>
+      <c r="E29" s="35"/>
+      <c r="F29" s="35"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="42"/>
+      <c r="I29" s="16"/>
+      <c r="J29" s="43"/>
+      <c r="K29" s="44"/>
+      <c r="L29" s="45"/>
+      <c r="M29" s="44"/>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="34"/>
+      <c r="B30" s="35"/>
+      <c r="C30" s="35"/>
+      <c r="D30" s="35"/>
+      <c r="E30" s="35"/>
+      <c r="F30" s="35"/>
+      <c r="G30" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="H30" s="46" t="s">
+        <v>22</v>
+      </c>
+      <c r="I30" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="J30" s="47"/>
+      <c r="K30" s="36"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="29" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="34"/>
+      <c r="B31" s="35"/>
+      <c r="C31" s="35"/>
+      <c r="D31" s="35"/>
+      <c r="E31" s="35"/>
+      <c r="F31" s="35"/>
+      <c r="G31" s="48"/>
+      <c r="H31" s="49"/>
+      <c r="I31" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="J31" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="K31" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="L31" s="51"/>
+      <c r="M31" s="29" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="34"/>
+      <c r="B32" s="35"/>
+      <c r="C32" s="35"/>
+      <c r="D32" s="35"/>
+      <c r="E32" s="35"/>
+      <c r="F32" s="35"/>
+      <c r="G32" s="52"/>
+      <c r="H32" s="15"/>
+      <c r="I32" s="50" t="s">
+        <v>29</v>
+      </c>
+      <c r="J32" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="K32" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="L32" s="53"/>
+      <c r="M32" s="11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="54"/>
+      <c r="B33" s="55"/>
+      <c r="C33" s="55"/>
+      <c r="D33" s="55"/>
+      <c r="E33" s="55"/>
+      <c r="F33" s="55"/>
+      <c r="G33" s="56"/>
+      <c r="H33" s="49"/>
+      <c r="I33" s="50" t="s">
+        <v>30</v>
+      </c>
+      <c r="J33" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="K33" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="L33" s="51"/>
+      <c r="M33" s="29" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="57" t="s">
+        <v>31</v>
+      </c>
+      <c r="B34" s="58"/>
+      <c r="C34" s="58"/>
+      <c r="D34" s="58"/>
+      <c r="E34" s="28"/>
+      <c r="F34" s="28"/>
+      <c r="G34" s="59" t="s">
+        <v>32</v>
+      </c>
+      <c r="H34" s="28"/>
+      <c r="I34" s="28"/>
+      <c r="J34" s="60"/>
+      <c r="K34" s="28"/>
+      <c r="L34" s="28"/>
+      <c r="M34" s="60"/>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="61"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="62" t="s">
+        <v>33</v>
+      </c>
+      <c r="H35" s="63"/>
+      <c r="I35" s="3"/>
+      <c r="J35" s="64"/>
+      <c r="K35" s="51" t="s">
+        <v>34</v>
+      </c>
+      <c r="L35" s="51"/>
+      <c r="M35" s="29" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="65" t="s">
+        <v>36</v>
+      </c>
+      <c r="B36" s="66"/>
+      <c r="C36" s="67" t="s">
+        <v>37</v>
+      </c>
+      <c r="D36" s="68"/>
+      <c r="E36" s="43"/>
+      <c r="F36" s="69"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="53"/>
+      <c r="I36" s="53"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="72" t="s">
+        <v>38</v>
+      </c>
+      <c r="L36" s="72"/>
+      <c r="M36" s="73"/>
+    </row>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="H41" s="25" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="49" ht="15.75" customHeight="1"/>
+    <row r="50" ht="15.75" customHeight="1"/>
+    <row r="51" ht="15.75" customHeight="1"/>
+    <row r="52" ht="15.75" customHeight="1"/>
+    <row r="53" ht="15.75" customHeight="1"/>
+    <row r="54" ht="15.75" customHeight="1"/>
+    <row r="55" ht="15.75" customHeight="1"/>
+    <row r="56" ht="15.75" customHeight="1"/>
+    <row r="57" ht="15.75" customHeight="1"/>
+    <row r="58" ht="15.75" customHeight="1"/>
+    <row r="59" ht="15.75" customHeight="1"/>
+    <row r="60" ht="15.75" customHeight="1"/>
+    <row r="61" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1"/>
+    <row r="63" ht="15.75" customHeight="1"/>
+    <row r="64" ht="15.75" customHeight="1"/>
+    <row r="65" ht="15.75" customHeight="1"/>
+    <row r="66" ht="15.75" customHeight="1"/>
+    <row r="67" ht="15.75" customHeight="1"/>
+    <row r="68" ht="15.75" customHeight="1"/>
+    <row r="69" ht="15.75" customHeight="1"/>
+    <row r="70" ht="15.75" customHeight="1"/>
+    <row r="71" ht="15.75" customHeight="1"/>
+    <row r="72" ht="15.75" customHeight="1"/>
+    <row r="73" ht="15.75" customHeight="1"/>
+    <row r="74" ht="15.75" customHeight="1"/>
+    <row r="75" ht="15.75" customHeight="1"/>
+    <row r="76" ht="15.75" customHeight="1"/>
+    <row r="77" ht="15.75" customHeight="1"/>
+    <row r="78" ht="15.75" customHeight="1"/>
+    <row r="79" ht="15.75" customHeight="1"/>
+    <row r="80" ht="15.75" customHeight="1"/>
+    <row r="81" ht="15.75" customHeight="1"/>
+    <row r="82" ht="15.75" customHeight="1"/>
+    <row r="83" ht="15.75" customHeight="1"/>
+    <row r="84" ht="15.75" customHeight="1"/>
+    <row r="85" ht="15.75" customHeight="1"/>
+    <row r="86" ht="15.75" customHeight="1"/>
+    <row r="87" ht="15.75" customHeight="1"/>
+    <row r="88" ht="15.75" customHeight="1"/>
+    <row r="89" ht="15.75" customHeight="1"/>
+    <row r="90" ht="15.75" customHeight="1"/>
+    <row r="91" ht="15.75" customHeight="1"/>
+    <row r="92" ht="15.75" customHeight="1"/>
+    <row r="93" ht="15.75" customHeight="1"/>
+    <row r="94" ht="15.75" customHeight="1"/>
+    <row r="95" ht="15.75" customHeight="1"/>
+    <row r="96" ht="15.75" customHeight="1"/>
+    <row r="97" ht="15.75" customHeight="1"/>
+    <row r="98" ht="15.75" customHeight="1"/>
+    <row r="99" ht="15.75" customHeight="1"/>
+    <row r="100" ht="15.75" customHeight="1"/>
+    <row r="101" ht="15.75" customHeight="1"/>
+    <row r="102" ht="15.75" customHeight="1"/>
+    <row r="103" ht="15.75" customHeight="1"/>
+    <row r="104" ht="15.75" customHeight="1"/>
+    <row r="105" ht="15.75" customHeight="1"/>
+    <row r="106" ht="15.75" customHeight="1"/>
+    <row r="107" ht="15.75" customHeight="1"/>
+    <row r="108" ht="15.75" customHeight="1"/>
+    <row r="109" ht="15.75" customHeight="1"/>
+    <row r="110" ht="15.75" customHeight="1"/>
+    <row r="111" ht="15.75" customHeight="1"/>
+    <row r="112" ht="15.75" customHeight="1"/>
+    <row r="113" ht="15.75" customHeight="1"/>
+    <row r="114" ht="15.75" customHeight="1"/>
+    <row r="115" ht="15.75" customHeight="1"/>
+    <row r="116" ht="15.75" customHeight="1"/>
+    <row r="117" ht="15.75" customHeight="1"/>
+    <row r="118" ht="15.75" customHeight="1"/>
+    <row r="119" ht="15.75" customHeight="1"/>
+    <row r="120" ht="15.75" customHeight="1"/>
+    <row r="121" ht="15.75" customHeight="1"/>
+    <row r="122" ht="15.75" customHeight="1"/>
+    <row r="123" ht="15.75" customHeight="1"/>
+    <row r="124" ht="15.75" customHeight="1"/>
+    <row r="125" ht="15.75" customHeight="1"/>
+    <row r="126" ht="15.75" customHeight="1"/>
+    <row r="127" ht="15.75" customHeight="1"/>
+    <row r="128" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="20">
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="E11:G11"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="E13:G13"/>
+    <mergeCell ref="E14:G14"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="E8:G8"/>
+  </mergeCells>
+  <printOptions/>
+  <pageMargins bottom="0.7874015748031497" footer="0.0" header="0.0" left="0.0" right="0.0" top="0.7874015748031497"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="11.0"/>
+    <col customWidth="1" min="2" max="2" width="10.43"/>
+    <col customWidth="1" min="3" max="3" width="9.43"/>
+    <col customWidth="1" min="4" max="6" width="10.71"/>
+    <col customWidth="1" min="7" max="7" width="10.43"/>
+    <col customWidth="1" min="8" max="26" width="10.71"/>
+  </cols>
+  <sheetData>
+    <row r="4">
+      <c r="G4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K4" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="3"/>
+      <c r="G5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H5" s="4"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="8"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="11"/>
+      <c r="J7" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L7" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="22"/>
+      <c r="J8" s="23"/>
+      <c r="K8" s="24"/>
+      <c r="L8" s="23"/>
+      <c r="M8" s="24"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="17"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="23"/>
+      <c r="K9" s="24"/>
+      <c r="L9" s="23"/>
+      <c r="M9" s="24"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="17"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="23"/>
+      <c r="K10" s="24"/>
+      <c r="L10" s="23"/>
+      <c r="M10" s="24"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="17"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="23"/>
+      <c r="K11" s="24"/>
+      <c r="L11" s="23"/>
+      <c r="M11" s="24"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="17"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="23"/>
+      <c r="K12" s="24"/>
+      <c r="L12" s="23"/>
+      <c r="M12" s="24"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="17"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="23"/>
+      <c r="K13" s="24"/>
+      <c r="L13" s="23"/>
+      <c r="M13" s="24"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="17"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="23"/>
+      <c r="K14" s="24"/>
+      <c r="L14" s="23"/>
+      <c r="M14" s="24"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="17"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="24"/>
+      <c r="L15" s="23"/>
+      <c r="M15" s="24"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="17"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="23"/>
+      <c r="K16" s="24"/>
+      <c r="L16" s="23"/>
+      <c r="M16" s="24"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="17"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="23"/>
+      <c r="K17" s="24"/>
+      <c r="L17" s="23"/>
+      <c r="M17" s="24"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="17"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="23"/>
+      <c r="K18" s="24"/>
+      <c r="L18" s="23"/>
+      <c r="M18" s="24"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="17"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="22"/>
+      <c r="J19" s="23"/>
+      <c r="K19" s="24"/>
+      <c r="L19" s="23"/>
+      <c r="M19" s="24"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="17"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="23"/>
+      <c r="K20" s="24"/>
+      <c r="L20" s="23"/>
+      <c r="M20" s="24"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="17"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="22"/>
+      <c r="J21" s="23"/>
+      <c r="K21" s="24"/>
+      <c r="L21" s="23"/>
+      <c r="M21" s="24"/>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="17"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="23"/>
+      <c r="K22" s="24"/>
+      <c r="L22" s="23"/>
+      <c r="M22" s="24"/>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="17"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="23"/>
+      <c r="K23" s="24"/>
+      <c r="L23" s="23"/>
+      <c r="M23" s="24"/>
+      <c r="Q23" s="25" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="17"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="22"/>
+      <c r="J24" s="23"/>
+      <c r="K24" s="24"/>
+      <c r="L24" s="23"/>
+      <c r="M24" s="24"/>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="17"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="22"/>
+      <c r="J25" s="23"/>
+      <c r="K25" s="24"/>
+      <c r="L25" s="23"/>
+      <c r="M25" s="24"/>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="17"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="23"/>
+      <c r="K26" s="24"/>
+      <c r="L26" s="23"/>
+      <c r="M26" s="24"/>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B27" s="27"/>
+      <c r="C27" s="28"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="28"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="I27" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="J27" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="K27" s="33"/>
+      <c r="L27" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="M27" s="29" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="34"/>
+      <c r="B28" s="35"/>
+      <c r="C28" s="35"/>
+      <c r="D28" s="35"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="35"/>
+      <c r="G28" s="36"/>
+      <c r="H28" s="37"/>
+      <c r="I28" s="38"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="39"/>
+      <c r="M28" s="40"/>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="34"/>
+      <c r="B29" s="35"/>
+      <c r="C29" s="35"/>
+      <c r="D29" s="35"/>
+      <c r="E29" s="35"/>
+      <c r="F29" s="35"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="42"/>
+      <c r="I29" s="16"/>
+      <c r="J29" s="43"/>
+      <c r="K29" s="44"/>
+      <c r="L29" s="45"/>
+      <c r="M29" s="44"/>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="34"/>
+      <c r="B30" s="35"/>
+      <c r="C30" s="35"/>
+      <c r="D30" s="35"/>
+      <c r="E30" s="35"/>
+      <c r="F30" s="35"/>
+      <c r="G30" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="H30" s="46" t="s">
+        <v>22</v>
+      </c>
+      <c r="I30" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="J30" s="47"/>
+      <c r="K30" s="36"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="29" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="34"/>
+      <c r="B31" s="35"/>
+      <c r="C31" s="35"/>
+      <c r="D31" s="35"/>
+      <c r="E31" s="35"/>
+      <c r="F31" s="35"/>
+      <c r="G31" s="48"/>
+      <c r="H31" s="49"/>
+      <c r="I31" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="J31" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="K31" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="L31" s="51"/>
+      <c r="M31" s="29" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="34"/>
+      <c r="B32" s="35"/>
+      <c r="C32" s="35"/>
+      <c r="D32" s="35"/>
+      <c r="E32" s="35"/>
+      <c r="F32" s="35"/>
+      <c r="G32" s="52"/>
+      <c r="H32" s="15"/>
+      <c r="I32" s="50" t="s">
+        <v>29</v>
+      </c>
+      <c r="J32" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="K32" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="L32" s="53"/>
+      <c r="M32" s="11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="54"/>
+      <c r="B33" s="55"/>
+      <c r="C33" s="55"/>
+      <c r="D33" s="55"/>
+      <c r="E33" s="55"/>
+      <c r="F33" s="55"/>
+      <c r="G33" s="56"/>
+      <c r="H33" s="49"/>
+      <c r="I33" s="50" t="s">
+        <v>30</v>
+      </c>
+      <c r="J33" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="K33" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="L33" s="51"/>
+      <c r="M33" s="29" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="57" t="s">
+        <v>31</v>
+      </c>
+      <c r="B34" s="58"/>
+      <c r="C34" s="58"/>
+      <c r="D34" s="58"/>
+      <c r="E34" s="28"/>
+      <c r="F34" s="28"/>
+      <c r="G34" s="59" t="s">
+        <v>32</v>
+      </c>
+      <c r="H34" s="28"/>
+      <c r="I34" s="28"/>
+      <c r="J34" s="60"/>
+      <c r="K34" s="28"/>
+      <c r="L34" s="28"/>
+      <c r="M34" s="60"/>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="61"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="62" t="s">
+        <v>33</v>
+      </c>
+      <c r="H35" s="63"/>
+      <c r="I35" s="3"/>
+      <c r="J35" s="64"/>
+      <c r="K35" s="51" t="s">
+        <v>34</v>
+      </c>
+      <c r="L35" s="51"/>
+      <c r="M35" s="29" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="65" t="s">
+        <v>36</v>
+      </c>
+      <c r="B36" s="66"/>
+      <c r="C36" s="67" t="s">
+        <v>37</v>
+      </c>
+      <c r="D36" s="68"/>
+      <c r="E36" s="43"/>
+      <c r="F36" s="69"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="53"/>
+      <c r="I36" s="53"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="72" t="s">
+        <v>38</v>
+      </c>
+      <c r="L36" s="72"/>
+      <c r="M36" s="73"/>
+    </row>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="H41" s="25" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="49" ht="15.75" customHeight="1"/>
+    <row r="50" ht="15.75" customHeight="1"/>
+    <row r="51" ht="15.75" customHeight="1"/>
+    <row r="52" ht="15.75" customHeight="1"/>
+    <row r="53" ht="15.75" customHeight="1"/>
+    <row r="54" ht="15.75" customHeight="1"/>
+    <row r="55" ht="15.75" customHeight="1"/>
+    <row r="56" ht="15.75" customHeight="1"/>
+    <row r="57" ht="15.75" customHeight="1"/>
+    <row r="58" ht="15.75" customHeight="1"/>
+    <row r="59" ht="15.75" customHeight="1"/>
+    <row r="60" ht="15.75" customHeight="1"/>
+    <row r="61" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1"/>
+    <row r="63" ht="15.75" customHeight="1"/>
+    <row r="64" ht="15.75" customHeight="1"/>
+    <row r="65" ht="15.75" customHeight="1"/>
+    <row r="66" ht="15.75" customHeight="1"/>
+    <row r="67" ht="15.75" customHeight="1"/>
+    <row r="68" ht="15.75" customHeight="1"/>
+    <row r="69" ht="15.75" customHeight="1"/>
+    <row r="70" ht="15.75" customHeight="1"/>
+    <row r="71" ht="15.75" customHeight="1"/>
+    <row r="72" ht="15.75" customHeight="1"/>
+    <row r="73" ht="15.75" customHeight="1"/>
+    <row r="74" ht="15.75" customHeight="1"/>
+    <row r="75" ht="15.75" customHeight="1"/>
+    <row r="76" ht="15.75" customHeight="1"/>
+    <row r="77" ht="15.75" customHeight="1"/>
+    <row r="78" ht="15.75" customHeight="1"/>
+    <row r="79" ht="15.75" customHeight="1"/>
+    <row r="80" ht="15.75" customHeight="1"/>
+    <row r="81" ht="15.75" customHeight="1"/>
+    <row r="82" ht="15.75" customHeight="1"/>
+    <row r="83" ht="15.75" customHeight="1"/>
+    <row r="84" ht="15.75" customHeight="1"/>
+    <row r="85" ht="15.75" customHeight="1"/>
+    <row r="86" ht="15.75" customHeight="1"/>
+    <row r="87" ht="15.75" customHeight="1"/>
+    <row r="88" ht="15.75" customHeight="1"/>
+    <row r="89" ht="15.75" customHeight="1"/>
+    <row r="90" ht="15.75" customHeight="1"/>
+    <row r="91" ht="15.75" customHeight="1"/>
+    <row r="92" ht="15.75" customHeight="1"/>
+    <row r="93" ht="15.75" customHeight="1"/>
+    <row r="94" ht="15.75" customHeight="1"/>
+    <row r="95" ht="15.75" customHeight="1"/>
+    <row r="96" ht="15.75" customHeight="1"/>
+    <row r="97" ht="15.75" customHeight="1"/>
+    <row r="98" ht="15.75" customHeight="1"/>
+    <row r="99" ht="15.75" customHeight="1"/>
+    <row r="100" ht="15.75" customHeight="1"/>
+    <row r="101" ht="15.75" customHeight="1"/>
+    <row r="102" ht="15.75" customHeight="1"/>
+    <row r="103" ht="15.75" customHeight="1"/>
+    <row r="104" ht="15.75" customHeight="1"/>
+    <row r="105" ht="15.75" customHeight="1"/>
+    <row r="106" ht="15.75" customHeight="1"/>
+    <row r="107" ht="15.75" customHeight="1"/>
+    <row r="108" ht="15.75" customHeight="1"/>
+    <row r="109" ht="15.75" customHeight="1"/>
+    <row r="110" ht="15.75" customHeight="1"/>
+    <row r="111" ht="15.75" customHeight="1"/>
+    <row r="112" ht="15.75" customHeight="1"/>
+    <row r="113" ht="15.75" customHeight="1"/>
+    <row r="114" ht="15.75" customHeight="1"/>
+    <row r="115" ht="15.75" customHeight="1"/>
+    <row r="116" ht="15.75" customHeight="1"/>
+    <row r="117" ht="15.75" customHeight="1"/>
+    <row r="118" ht="15.75" customHeight="1"/>
+    <row r="119" ht="15.75" customHeight="1"/>
+    <row r="120" ht="15.75" customHeight="1"/>
+    <row r="121" ht="15.75" customHeight="1"/>
+    <row r="122" ht="15.75" customHeight="1"/>
+    <row r="123" ht="15.75" customHeight="1"/>
+    <row r="124" ht="15.75" customHeight="1"/>
+    <row r="125" ht="15.75" customHeight="1"/>
+    <row r="126" ht="15.75" customHeight="1"/>
+    <row r="127" ht="15.75" customHeight="1"/>
+    <row r="128" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="20">
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="E11:G11"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="E13:G13"/>
+    <mergeCell ref="E14:G14"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="E15:G15"/>
+  </mergeCells>
+  <printOptions/>
+  <pageMargins bottom="0.7874015748031497" footer="0.0" header="0.0" left="0.0" right="0.0" top="0.7874015748031497"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <sheetData/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>